--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107857</v>
+        <v>107860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98207</v>
+        <v>98210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107860</v>
+        <v>107861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98210</v>
+        <v>98211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136547873</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107861</v>
+        <v>107866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>98216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107866</v>
+        <v>107868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98216</v>
+        <v>98218</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107868</v>
+        <v>107874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107874</v>
+        <v>107876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107876</v>
+        <v>107877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107877</v>
+        <v>107883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107883</v>
+        <v>107887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107887</v>
+        <v>107889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107889</v>
+        <v>107891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136547873</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107891</v>
+        <v>107904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 64310-2021 artfynd.xlsx
+++ b/artfynd/A 64310-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136547873</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136543570</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136545916</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136545917</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136545684</v>
       </c>
       <c r="B6" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136543043</v>
       </c>
       <c r="B7" t="n">
-        <v>107904</v>
+        <v>107906</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136545525</v>
       </c>
       <c r="B8" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
